--- a/app/reports/NTIP_research.xlsx
+++ b/app/reports/NTIP_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-28 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.6243</v>
+        <v>1.5892</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04595999717712403</v>
+        <v>0.05015999794006348</v>
       </c>
     </row>
     <row r="6">
@@ -1172,7 +1172,7 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>34589000</v>
+        <v>33752000</v>
       </c>
     </row>
     <row r="34">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22944827.92587576</v>
+        <v>22863181.47495595</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.6243</v>
+        <v>1.5892</v>
       </c>
     </row>
     <row r="38">
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>37269284</v>
+        <v>36334168</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>-0.51</v>
+        <v>-0.46</v>
       </c>
       <c r="F5" s="31" t="n"/>
     </row>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>36502260</v>
+        <v>34515424</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>15.900001</v>
+        <v>14.883721</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>8.781000000000001</v>
+        <v>4.853</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.672</v>
+        <v>0.501</v>
       </c>
     </row>
     <row r="7">
@@ -1537,16 +1537,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>66378588</v>
+        <v>65056192</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>41.875</v>
+        <v>16.931034</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>28.317</v>
+        <v>14.799</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.273</v>
+        <v>1.271</v>
       </c>
     </row>
     <row r="8">
@@ -1561,14 +1561,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>70240288</v>
-      </c>
-      <c r="D8" s="33" t="n"/>
+        <v>129312208</v>
+      </c>
+      <c r="D8" s="33" t="n">
+        <v>13.5465765</v>
+      </c>
       <c r="E8" s="33" t="n">
-        <v>8.731999999999999</v>
+        <v>7.458</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>2.904</v>
+        <v>3.399</v>
       </c>
     </row>
     <row r="9">
@@ -1583,14 +1585,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>18009100</v>
+        <v>11476255</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-10.767</v>
+        <v>-10.019</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>2.34</v>
+        <v>2.082</v>
       </c>
     </row>
     <row r="10">
@@ -1605,14 +1607,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>20730900</v>
+        <v>6654815</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-3.367</v>
+        <v>-1.548</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.132</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="11">
@@ -1627,14 +1629,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>11660079</v>
+        <v>14595820</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-1.121</v>
+        <v>-0.945</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>8.050000000000001</v>
+        <v>4.263</v>
       </c>
     </row>
     <row r="12">
@@ -1649,14 +1651,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>28027772</v>
+        <v>24573176</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>12.309</v>
+        <v>11.001</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.374</v>
+        <v>0.346</v>
       </c>
     </row>
     <row r="13">
@@ -1671,14 +1673,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>14204959</v>
+        <v>19878992</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-3.483</v>
+        <v>-5.128</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.287</v>
+        <v>0.396</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/NTIP_research.xlsx
+++ b/app/reports/NTIP_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-28 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-29 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.5892</v>
+        <v>1.58</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.05015999794006348</v>
+        <v>0.04994999885559082</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22863181.47495595</v>
+        <v>22863179.74683544</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.5892</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="38">
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>36334168</v>
+        <v>36123824</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>-0.46</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F5" s="31" t="n"/>
     </row>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>34515424</v>
+        <v>33490748</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>14.883721</v>
+        <v>14.44186</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>4.853</v>
+        <v>4.873</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.501</v>
+        <v>0.503</v>
       </c>
     </row>
     <row r="7">
@@ -1537,16 +1537,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>65056192</v>
+        <v>65322512</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>16.931034</v>
+        <v>17.000345</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>14.799</v>
+        <v>14.611</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.271</v>
+        <v>1.255</v>
       </c>
     </row>
     <row r="8">
@@ -1561,16 +1561,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>129312208</v>
+        <v>132393512</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>13.5465765</v>
+        <v>13.86937</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>7.458</v>
+        <v>7.506</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3.399</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="9">
@@ -1585,14 +1585,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>11476255</v>
+        <v>12000228</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-10.019</v>
+        <v>-10.089</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>2.082</v>
+        <v>2.096</v>
       </c>
     </row>
     <row r="10">
@@ -1607,14 +1607,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>6654815</v>
+        <v>6865849</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-1.548</v>
+        <v>-1.527</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.049</v>
+        <v>0.048</v>
       </c>
     </row>
     <row r="11">
@@ -1629,14 +1629,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>14595820</v>
+        <v>15152822</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-0.945</v>
+        <v>-0.952</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>4.263</v>
+        <v>4.294</v>
       </c>
     </row>
     <row r="12">
@@ -1651,14 +1651,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>24573176</v>
+        <v>23413070</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>11.001</v>
+        <v>11.055</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.346</v>
+        <v>0.348</v>
       </c>
     </row>
     <row r="13">
@@ -1673,14 +1673,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>19878992</v>
+        <v>16755150</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-5.128</v>
+        <v>-5.045</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.396</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/NTIP_research.xlsx
+++ b/app/reports/NTIP_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-29 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04994999885559082</v>
+        <v>0.04933000087738037</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22863179.74683544</v>
+        <v>22863179.87421384</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="38">
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>36123824</v>
+        <v>36352456</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.62</v>
       </c>
       <c r="F5" s="31" t="n"/>
     </row>
@@ -1513,13 +1513,13 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>33490748</v>
+        <v>33167166</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>14.44186</v>
+        <v>14.302325</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>4.873</v>
+        <v>4.866</v>
       </c>
       <c r="F6" s="33" t="n">
         <v>0.503</v>
@@ -1537,16 +1537,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>65322512</v>
+        <v>65720008</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>17.000345</v>
+        <v>17.103794</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>14.611</v>
+        <v>14.716</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.255</v>
+        <v>1.264</v>
       </c>
     </row>
     <row r="8">
@@ -1561,16 +1561,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>132393512</v>
+        <v>125399024</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>13.86937</v>
+        <v>13.136637</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>7.506</v>
+        <v>7.383</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3.42</v>
+        <v>3.365</v>
       </c>
     </row>
     <row r="9">
@@ -1585,14 +1585,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>12000228</v>
+        <v>11118421</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-10.089</v>
+        <v>-10.064</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>2.096</v>
+        <v>2.091</v>
       </c>
     </row>
     <row r="10">
@@ -1607,14 +1607,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>6865849</v>
+        <v>6076638</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-1.527</v>
+        <v>-1.405</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.048</v>
+        <v>0.044</v>
       </c>
     </row>
     <row r="11">
@@ -1629,14 +1629,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>15152822</v>
+        <v>14292529</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-0.952</v>
+        <v>-0.954</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>4.294</v>
+        <v>4.301</v>
       </c>
     </row>
     <row r="12">
@@ -1651,14 +1651,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>23413070</v>
+        <v>22991214</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>11.055</v>
+        <v>10.839</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.348</v>
+        <v>0.341</v>
       </c>
     </row>
     <row r="13">
@@ -1673,14 +1673,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>16755150</v>
+        <v>19421776</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-5.045</v>
+        <v>-5.083</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>0.39</v>
+        <v>0.392</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/NTIP_research.xlsx
+++ b/app/reports/NTIP_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-30 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-10-31 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04933000087738037</v>
+        <v>0.04928999900817871</v>
       </c>
     </row>
     <row r="6">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>22863179.87421384</v>
+        <v>22863179.22077922</v>
       </c>
     </row>
     <row r="36">
@@ -1214,7 +1214,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="38">
@@ -1493,11 +1493,11 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>36352456</v>
+        <v>35209296</v>
       </c>
       <c r="D5" s="31" t="n"/>
       <c r="E5" s="31" t="n">
-        <v>-0.62</v>
+        <v>-0.35</v>
       </c>
       <c r="F5" s="31" t="n"/>
     </row>
@@ -1513,16 +1513,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>33167166</v>
+        <v>31603186</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>14.302325</v>
+        <v>13.627907</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>4.866</v>
+        <v>4.648</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.503</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="7">
@@ -1537,16 +1537,16 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>65720008</v>
+        <v>63731220</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>17.103794</v>
+        <v>16.586206</v>
       </c>
       <c r="E7" s="33" t="n">
-        <v>14.716</v>
+        <v>14.401</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>1.264</v>
+        <v>1.237</v>
       </c>
     </row>
     <row r="8">
@@ -1561,16 +1561,16 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>125399024</v>
+        <v>127018648</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>13.136637</v>
+        <v>13.306307</v>
       </c>
       <c r="E8" s="33" t="n">
-        <v>7.383</v>
+        <v>7.335</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>3.365</v>
+        <v>3.343</v>
       </c>
     </row>
     <row r="9">
@@ -1585,14 +1585,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>11118421</v>
+        <v>11527376</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>-10.064</v>
+        <v>-10.017</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>2.091</v>
+        <v>2.081</v>
       </c>
     </row>
     <row r="10">
@@ -1607,14 +1607,14 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>6076638</v>
+        <v>6189382</v>
       </c>
       <c r="D10" s="33" t="n"/>
       <c r="E10" s="33" t="n">
-        <v>-1.405</v>
+        <v>-1.354</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>0.044</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="11">
@@ -1629,14 +1629,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>14292529</v>
+        <v>14336273</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-0.954</v>
+        <v>-0.906</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>4.301</v>
+        <v>4.087</v>
       </c>
     </row>
     <row r="12">
@@ -1655,10 +1655,10 @@
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>10.839</v>
+        <v>10.785</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.341</v>
+        <v>0.339</v>
       </c>
     </row>
     <row r="13">
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>19421776</v>
+        <v>16192860</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-5.083</v>
+        <v>-5.072</v>
       </c>
       <c r="F13" s="33" t="n">
         <v>0.392</v>
